--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 106 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 103 clubs short</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3313,8 +3313,8 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4204,8 +4204,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -8346,16 +8346,16 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="9" t="n">
         <v>0</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -19316,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="S192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192" s="10" t="n">
         <v>1</v>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -19415,8 +19415,8 @@
       <c r="S193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T193" s="9" t="n">
-        <v>0</v>
+      <c r="T193" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U193" s="9" t="n">
         <v>0</v>
@@ -20277,7 +20277,7 @@
         </is>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q202" s="9" t="n">
         <v>0</v>
@@ -23185,7 +23185,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -23251,7 +23251,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23581,7 +23581,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -24241,7 +24241,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 103 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 88 clubs short</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3995,8 +3995,8 @@
       <c r="T34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
+      <c r="U34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V34" s="9" t="n">
         <v>2</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6726,8 +6726,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8072,8 +8072,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10106,8 +10106,8 @@
       <c r="T97" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
+      <c r="U97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V97" s="10" t="n">
         <v>4</v>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11382,8 +11382,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="9" t="n">
         <v>0</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12352,8 +12352,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13886,8 +13886,8 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14098,8 +14098,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14583,8 +14583,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15650,8 +15650,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16011,8 +16011,8 @@
       <c r="P158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" s="9" t="n">
-        <v>1</v>
+      <c r="Q158" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R158" s="9" t="n">
         <v>0</v>
@@ -19072,7 +19072,7 @@
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -19142,8 +19142,8 @@
       <c r="Y190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z190" s="9" t="n">
-        <v>0</v>
+      <c r="Z190" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA190" s="10" t="n">
         <v>1</v>
@@ -20818,7 +20818,7 @@
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F208" s="6" t="n">
         <v>10</v>
@@ -20873,8 +20873,8 @@
       <c r="T208" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U208" s="9" t="n">
-        <v>0</v>
+      <c r="U208" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V208" s="10" t="n">
         <v>4</v>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>10</v>
@@ -21373,8 +21373,8 @@
       <c r="Y213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z213" s="9" t="n">
-        <v>0</v>
+      <c r="Z213" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA213" s="10" t="n">
         <v>1</v>
@@ -21400,7 +21400,7 @@
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" s="6" t="n">
         <v>10</v>
@@ -21470,8 +21470,8 @@
       <c r="Y214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z214" s="9" t="n">
-        <v>0</v>
+      <c r="Z214" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA214" s="10" t="n">
         <v>1</v>
@@ -21735,7 +21735,7 @@
         <v>0</v>
       </c>
       <c r="Q217" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R217" s="9" t="n">
         <v>0</v>
@@ -23251,7 +23251,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23350,7 +23350,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -23416,7 +23416,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -23449,7 +23449,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -23515,7 +23515,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23647,7 +23647,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -23746,7 +23746,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -23779,7 +23779,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -23812,7 +23812,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -23845,7 +23845,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -23911,7 +23911,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -23944,7 +23944,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -24010,7 +24010,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24043,7 +24043,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -24241,7 +24241,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -24340,7 +24340,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -24373,7 +24373,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -24406,7 +24406,7 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 52 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="7" t="n">
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8</v>
+        <v>-13</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>6</v>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2305,17 +2305,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2499,17 +2499,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-35</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2931,11 +2931,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>6</v>
@@ -2984,17 +2984,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="7" t="n">
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3469,17 +3469,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>1</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M33" s="7" t="n">
@@ -3902,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>1</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5356,11 +5356,11 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>3</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>4</v>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -5726,26 +5726,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P52" s="9" t="n">
+      <c r="P52" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="Q52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5841,8 +5841,8 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>2</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -6767,17 +6767,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -6961,17 +6961,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="8" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7190,8 +7190,8 @@
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="9" t="n">
-        <v>1</v>
+      <c r="S67" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T67" s="10" t="n">
         <v>1</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7393,11 +7393,11 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>1</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" s="9" t="n">
         <v>2</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="7" t="n">
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="7" t="n">
@@ -7864,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -7878,11 +7878,11 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>2</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>7</v>
@@ -7931,17 +7931,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="7" t="n">
@@ -7979,7 +7979,7 @@
         <v>4</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>5</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8125,17 +8125,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="7" t="n">
@@ -8363,14 +8363,14 @@
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>3</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>3</v>
+      <c r="X79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -8551,8 +8551,8 @@
       <c r="S81" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9095,17 +9095,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q89" s="9" t="n">
         <v>0</v>
@@ -9333,8 +9333,8 @@
       <c r="U89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>2</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9610,13 +9610,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="9" t="n">
-        <v>1</v>
+      <c r="S92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q93" s="10" t="n">
         <v>2</v>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -9916,13 +9916,13 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9968,17 +9968,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L101" s="8" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10488,14 +10488,14 @@
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="9" t="n">
-        <v>1</v>
+      <c r="S101" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U101" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V101" s="10" t="n">
         <v>4</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>1</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="7" t="n">
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10885,8 +10885,8 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>1</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -10938,17 +10938,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="7" t="n">
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11079,11 +11079,11 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X107" s="9" t="n">
         <v>3</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11273,8 +11273,8 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>2</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="8" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -11841,7 +11841,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12243,11 +12243,11 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X119" s="10" t="n">
         <v>5</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12625,8 +12625,8 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>1</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="8" t="inlineStr">
         <is>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>73</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>7</v>
+        <v>-23</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13604,8 +13604,8 @@
       <c r="V133" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W133" s="9" t="n">
-        <v>3</v>
+      <c r="W133" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X133" s="9" t="n">
         <v>3</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -13993,7 +13993,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="9" t="n">
         <v>2</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="7" t="n">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -14474,11 +14474,11 @@
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>3</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>4</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>4</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15056,11 +15056,11 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="9" t="n">
+      <c r="V148" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W148" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>5</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" s="8" t="inlineStr">
         <is>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -15251,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="7" t="n">
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -15691,17 +15691,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="7" t="n">
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L160" s="8" t="inlineStr">
         <is>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L161" s="8" t="inlineStr">
         <is>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L162" s="8" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16564,17 +16564,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L164" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="7" t="n">
@@ -16661,17 +16661,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -16691,7 +16691,7 @@
         <v>4</v>
       </c>
       <c r="Q165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -16855,17 +16855,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="8" t="inlineStr">
         <is>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L170" s="8" t="inlineStr">
         <is>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L171" s="8" t="inlineStr">
         <is>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L172" s="8" t="inlineStr">
         <is>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L173" s="8" t="inlineStr">
         <is>
@@ -17534,17 +17534,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-29</v>
+      </c>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="7" t="n">
@@ -17631,17 +17631,17 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L175" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M175" s="7" t="n">
@@ -17676,7 +17676,7 @@
         <v>1</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>0</v>
       </c>
       <c r="V176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L177" s="8" t="inlineStr">
         <is>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X178" s="10" t="n">
         <v>7</v>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L179" s="8" t="inlineStr">
         <is>
@@ -18213,17 +18213,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L181" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M181" s="7" t="n">
@@ -18310,17 +18310,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-43</v>
+      </c>
+      <c r="L182" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M182" s="7" t="n">
@@ -18407,17 +18407,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L183" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M183" s="7" t="n">
@@ -18504,13 +18504,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L184" s="8" t="inlineStr">
         <is>
@@ -18601,13 +18601,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L186" s="8" t="inlineStr">
         <is>
@@ -18795,13 +18795,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L187" s="8" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -18892,17 +18892,17 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L188" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M188" s="7" t="n">
@@ -18936,8 +18936,8 @@
       <c r="U188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V188" s="9" t="n">
-        <v>0</v>
+      <c r="V188" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L189" s="8" t="inlineStr">
         <is>
@@ -19086,17 +19086,17 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L190" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M190" s="7" t="n">
@@ -19183,13 +19183,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L191" s="8" t="inlineStr">
         <is>
@@ -19280,17 +19280,17 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L192" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L192" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M192" s="7" t="n">
@@ -19325,7 +19325,7 @@
         <v>0</v>
       </c>
       <c r="V192" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
@@ -19377,17 +19377,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L193" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M193" s="7" t="n">
@@ -19474,13 +19474,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L194" s="8" t="inlineStr">
         <is>
@@ -19571,13 +19571,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
@@ -19668,13 +19668,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
@@ -19765,13 +19765,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -19891,8 +19891,8 @@
       <c r="P198" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q198" s="9" t="n">
-        <v>1</v>
+      <c r="Q198" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R198" s="9" t="n">
         <v>0</v>
@@ -19906,11 +19906,11 @@
       <c r="U198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="9" t="n">
-        <v>3</v>
+      <c r="V198" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W198" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X198" s="10" t="n">
         <v>6</v>
@@ -19959,13 +19959,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L199" s="8" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L200" s="8" t="inlineStr">
         <is>
@@ -20100,8 +20100,8 @@
       <c r="U200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V200" s="9" t="n">
-        <v>2</v>
+      <c r="V200" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
@@ -20153,13 +20153,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L201" s="8" t="inlineStr">
         <is>
@@ -20250,13 +20250,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L202" s="8" t="inlineStr">
         <is>
@@ -20347,13 +20347,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L203" s="8" t="inlineStr">
         <is>
@@ -20444,13 +20444,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L204" s="8" t="inlineStr">
         <is>
@@ -20541,17 +20541,17 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L205" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L205" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M205" s="7" t="n">
@@ -20571,7 +20571,7 @@
         <v>0</v>
       </c>
       <c r="Q205" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R205" s="9" t="n">
         <v>0</v>
@@ -20638,13 +20638,13 @@
         </is>
       </c>
       <c r="I206" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>2</v>
       </c>
       <c r="Q206" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R206" s="9" t="n">
         <v>0</v>
@@ -20686,7 +20686,7 @@
         <v>4</v>
       </c>
       <c r="W206" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X206" s="10" t="n">
         <v>6</v>
@@ -20735,13 +20735,13 @@
         </is>
       </c>
       <c r="I207" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>0</v>
       </c>
       <c r="V207" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W207" s="9" t="n">
         <v>0</v>
@@ -20832,13 +20832,13 @@
         </is>
       </c>
       <c r="I208" s="4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K208" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="P208" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q208" s="9" t="n">
         <v>0</v>
@@ -20880,7 +20880,7 @@
         <v>4</v>
       </c>
       <c r="W208" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X208" s="10" t="n">
         <v>7</v>
@@ -20929,13 +20929,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L209" s="8" t="inlineStr">
         <is>
@@ -21026,17 +21026,17 @@
         </is>
       </c>
       <c r="I210" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J210" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K210" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L210" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L210" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M210" s="7" t="n">
@@ -21206,7 +21206,7 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>10</v>
@@ -21220,13 +21220,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -21249,8 +21249,8 @@
       <c r="P212" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q212" s="9" t="n">
-        <v>1</v>
+      <c r="Q212" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R212" s="9" t="n">
         <v>0</v>
@@ -21267,8 +21267,8 @@
       <c r="V212" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W212" s="9" t="n">
-        <v>1</v>
+      <c r="W212" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X212" s="10" t="n">
         <v>6</v>
@@ -21317,17 +21317,17 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L213" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M213" s="7" t="n">
@@ -21362,7 +21362,7 @@
         <v>0</v>
       </c>
       <c r="V213" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W213" s="9" t="n">
         <v>0</v>
@@ -21414,13 +21414,13 @@
         </is>
       </c>
       <c r="I214" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J214" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" s="8" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>0</v>
       </c>
       <c r="V214" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W214" s="9" t="n">
         <v>0</v>
@@ -21497,7 +21497,7 @@
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>10</v>
@@ -21511,13 +21511,13 @@
         </is>
       </c>
       <c r="I215" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
@@ -21555,11 +21555,11 @@
       <c r="U215" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V215" s="9" t="n">
-        <v>3</v>
+      <c r="V215" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W215" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X215" s="10" t="n">
         <v>6</v>
@@ -21594,7 +21594,7 @@
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>10</v>
@@ -21608,13 +21608,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L216" s="8" t="inlineStr">
         <is>
@@ -21652,11 +21652,11 @@
       <c r="U216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V216" s="9" t="n">
-        <v>3</v>
+      <c r="V216" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W216" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X216" s="10" t="n">
         <v>5</v>
@@ -21705,13 +21705,13 @@
         </is>
       </c>
       <c r="I217" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K217" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L217" s="8" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="P217" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q217" s="9" t="n">
         <v>1</v>
@@ -21802,13 +21802,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L218" s="8" t="inlineStr">
         <is>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="I219" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L219" s="8" t="inlineStr">
         <is>
@@ -21996,13 +21996,13 @@
         </is>
       </c>
       <c r="I220" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L220" s="8" t="inlineStr">
         <is>
@@ -22093,13 +22093,13 @@
         </is>
       </c>
       <c r="I221" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K221" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L221" s="8" t="inlineStr">
         <is>
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J222" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K222" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L222" s="8" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>0</v>
       </c>
       <c r="V223" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W223" s="9" t="n">
         <v>0</v>
@@ -22384,13 +22384,13 @@
         </is>
       </c>
       <c r="I224" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J224" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L224" s="8" t="inlineStr">
         <is>
@@ -22481,13 +22481,13 @@
         </is>
       </c>
       <c r="I225" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J225" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L225" s="8" t="inlineStr">
         <is>
@@ -22578,13 +22578,13 @@
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
@@ -22675,13 +22675,13 @@
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L227" s="8" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>0</v>
       </c>
       <c r="V227" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W227" s="9" t="n">
         <v>0</v>
@@ -22772,13 +22772,13 @@
         </is>
       </c>
       <c r="I228" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K228" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L228" s="8" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>0</v>
       </c>
       <c r="Q228" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R228" s="9" t="n">
         <v>0</v>
@@ -22869,17 +22869,17 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L229" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L229" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M229" s="7" t="n">
@@ -22914,7 +22914,7 @@
         <v>1</v>
       </c>
       <c r="V229" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W229" s="9" t="n">
         <v>0</v>
@@ -23068,7 +23068,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -23101,7 +23101,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -23167,7 +23167,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -23185,7 +23185,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -23200,7 +23200,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23233,7 +23233,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -23266,7 +23266,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -23317,7 +23317,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23332,7 +23332,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -23350,7 +23350,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -23365,7 +23365,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -23431,7 +23431,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -23449,7 +23449,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -23464,7 +23464,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -23482,7 +23482,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -23497,7 +23497,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -23515,7 +23515,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23530,7 +23530,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23548,7 +23548,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -23563,7 +23563,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -23614,13 +23614,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -23662,7 +23662,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -23680,13 +23680,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -23695,7 +23695,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -23713,7 +23713,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -23728,7 +23728,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -23746,7 +23746,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -23779,7 +23779,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -23794,7 +23794,7 @@
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -23812,7 +23812,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -23827,7 +23827,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23878,7 +23878,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -23893,7 +23893,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -23926,7 +23926,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -23944,7 +23944,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -23959,7 +23959,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -23977,7 +23977,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -24025,7 +24025,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -24058,7 +24058,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -24091,7 +24091,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -24124,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -24157,7 +24157,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -24190,7 +24190,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -24208,7 +24208,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -24223,7 +24223,7 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -24256,7 +24256,7 @@
         <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -24274,7 +24274,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -24307,7 +24307,7 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -24355,7 +24355,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -24373,13 +24373,13 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -24388,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -24406,13 +24406,13 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -24487,7 +24487,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/221/inyear.xlsx
+++ b/docs/d/221/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 52 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1379,8 +1379,8 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>3</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-35</v>
+        <v>-34</v>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3313,8 +3313,8 @@
       <c r="S27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
@@ -3810,8 +3810,8 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>3</v>
+      <c r="X32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -3901,8 +3901,8 @@
       <c r="U33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V33" s="9" t="n">
-        <v>3</v>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4465,8 +4465,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
-        <v>3</v>
+      <c r="P39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="X43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5347,8 +5347,8 @@
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="9" t="n">
-        <v>1</v>
+      <c r="S48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -6121,7 +6121,7 @@
         <v>2</v>
       </c>
       <c r="R56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>1</v>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7834,17 +7834,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M74" s="7" t="n">
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8457,8 +8457,8 @@
       <c r="T80" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U80" s="9" t="n">
-        <v>0</v>
+      <c r="U80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V80" s="10" t="n">
         <v>4</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>1</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>68</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>7</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9818,8 +9818,8 @@
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>2</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="8" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -11564,8 +11564,8 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>2</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -12632,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q129" s="10" t="n">
         <v>2</v>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L142" s="8" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>4</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-23</v>
+        <v>-18</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L153" s="8" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L157" s="8" t="inlineStr">
         <is>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" s="8" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>1</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L164" s="8" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L167" s="8" t="inlineStr">
         <is>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -17370,13 +17370,13 @@
         <v>0</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T172" s="9" t="n">
         <v>0</v>
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L176" s="8" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q178" s="10" t="n">
         <v>2</v>
@@ -18440,7 +18440,7 @@
         <v>2</v>
       </c>
       <c r="R183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S183" s="9" t="n">
         <v>0</v>
@@ -18504,13 +18504,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="L184" s="8" t="inlineStr">
         <is>
@@ -18601,13 +18601,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185" s="8" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>0</v>
       </c>
       <c r="V185" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W185" s="9" t="n">
         <v>0</v>
@@ -18892,13 +18892,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L188" s="8" t="inlineStr">
         <is>
@@ -19280,13 +19280,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L192" s="8" t="inlineStr">
         <is>
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L200" s="8" t="inlineStr">
         <is>
@@ -20929,13 +20929,13 @@
         </is>
       </c>
       <c r="I209" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K209" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L209" s="8" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="P210" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q210" s="9" t="n">
         <v>1</v>
@@ -21220,13 +21220,13 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K212" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
@@ -21367,8 +21367,8 @@
       <c r="W213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X213" s="9" t="n">
-        <v>2</v>
+      <c r="X213" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y213" s="9" t="n">
         <v>0</v>
@@ -21608,13 +21608,13 @@
         </is>
       </c>
       <c r="I216" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K216" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L216" s="8" t="inlineStr">
         <is>
@@ -21802,13 +21802,13 @@
         </is>
       </c>
       <c r="I218" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K218" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L218" s="8" t="inlineStr">
         <is>
@@ -22869,13 +22869,13 @@
         </is>
       </c>
       <c r="I229" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K229" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L229" s="8" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -23218,7 +23218,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -23251,13 +23251,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -23284,7 +23284,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -23317,7 +23317,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23530,7 +23530,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -23548,13 +23548,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -23629,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -23647,7 +23647,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -23746,7 +23746,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
